--- a/docs/总题库包含出现题库名.xlsx
+++ b/docs/总题库包含出现题库名.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Hamwiki\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B72C5480-06EE-489B-95D5-B6930FC268F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A8DB95B-840B-45CD-AB54-DA26D0F68F27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22774,60 +22774,60 @@
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
+      <c r="A36" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="B36" t="s">
+      <c r="B36" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="C36" t="s">
+      <c r="C36" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="D36" t="s">
+      <c r="D36" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="E36" t="s">
+      <c r="E36" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="F36" t="s">
+      <c r="F36" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="G36" t="s">
+      <c r="G36" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="H36" t="s">
+      <c r="H36" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="I36" t="s">
+      <c r="I36" s="1" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
+      <c r="A37" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="B37" t="s">
+      <c r="B37" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="C37" t="s">
+      <c r="C37" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="D37" t="s">
+      <c r="D37" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="E37" t="s">
-        <v>5</v>
-      </c>
-      <c r="F37" t="s">
+      <c r="E37" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F37" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="G37" t="s">
+      <c r="G37" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="H37" t="s">
+      <c r="H37" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="I37" t="s">
+      <c r="I37" s="1" t="s">
         <v>212</v>
       </c>
     </row>
